--- a/results/05_transient_transcription_output/905/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,137 +626,119 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
-</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n"/>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -772,8 +754,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
-</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -783,8 +764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -794,122 +774,102 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -926,141 +886,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4944
-</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1077,141 +1014,118 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3844
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1228,146 +1142,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4602
-</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1384,56 +1274,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
-</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6717
-</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1443,81 +1324,68 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433
-</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12721
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3842
-</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">927
-</t>
+          <t>927</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>031</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4451
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,141 +1402,118 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281
-</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104 14
-</t>
+          <t>01 214 1</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 14
-</t>
+          <t>181 14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,44 +1530,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
-</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1733,87 +1571,73 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,146 +1654,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,141 +1786,118 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
-</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
-</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2137,141 +1914,118 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2
-</t>
+          <t>1 21 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2288,146 +2042,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9085
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,140 +2174,117 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13618
-</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1099
-</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10893
-</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043
-</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21166
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
-</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">351
-</t>
+          <t>351</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0987
-</t>
+          <t>097</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4584
-</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr"/>
@@ -2595,146 +2302,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23124
-</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9401
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21891
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7891
-</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12116
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 12 1
-</t>
+          <t>20 2 2</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 884
-</t>
+          <t>226 214</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 11
-</t>
+          <t>14 214</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2751,38 +2434,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3546
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2797,38 +2474,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2838,50 +2509,42 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -2899,146 +2562,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194
-</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3060,32 +2699,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3095,104 +2729,87 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18918
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3209,8 +2826,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22842
-</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3220,129 +2836,108 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3359,146 +2954,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3392
-</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3515,56 +3086,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15426
-</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
-</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3526
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3574,14 +3136,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3594,50 +3154,42 @@
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
-</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2931
-</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6068
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3654,56 +3206,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11848
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3713,81 +3256,68 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2101
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881811
-</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3809,58 +3339,49 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3870,68 +3391,57 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3948,146 +3458,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3411
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4104,146 +3590,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
-</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4260,51 +3722,43 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">453
-</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4314,86 +3768,72 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
-</t>
+          <t>747</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28641
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4410,146 +3850,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4566,146 +3982,122 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1788
-</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1064
-</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7107
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14345
-</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 82
-</t>
+          <t>2 89</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161
-</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4722,136 +4114,114 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3577
-</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9631
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 9
-</t>
+          <t>3 9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13721
-</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184415 18
-</t>
+          <t>2611 4</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4873,38 +4243,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 7
-</t>
+          <t>21 7</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 118
-</t>
+          <t>13 01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4916,81 +4280,68 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5007,38 +4358,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2251
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5048,104 +4393,87 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>774</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5162,146 +4490,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3502
-</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5318,146 +4622,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
-</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
-</t>
+          <t>895</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5474,146 +4754,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5630,44 +4886,37 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643
-</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7106
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -5678,87 +4927,73 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8998
-</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93834
-</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9231
-</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>0294</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187
-</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5775,141 +5010,118 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
-</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16889
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02251
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20971
-</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89718
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5926,8 +5138,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
-</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5937,27 +5148,23 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -5967,8 +5174,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5978,65 +5184,55 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -6054,146 +5250,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6210,8 +5382,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
-</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -6221,99 +5392,83 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10169
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -6323,26 +5478,22 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6364,135 +5515,113 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6820
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6509,141 +5638,118 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7426
-</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2885
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
-</t>
+          <t>555</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2185
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6660,8 +5766,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6701,141 +5806,118 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18890
-</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
+          <t>697</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14055
-</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12684
-</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300
-</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
-</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6852,32 +5934,27 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
-</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6887,110 +5964,92 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
